--- a/AAII_Financials/Yearly/BDC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BDC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>BDC</t>
   </si>
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="E14" s="3">
         <v>16800</v>
@@ -1250,8 +1250,8 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
+      <c r="D20" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>51</v>
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>373900</v>
+        <v>374000</v>
       </c>
       <c r="E21" s="3">
         <v>331900</v>
@@ -1862,8 +1862,8 @@
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
+      <c r="D32" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>51</v>
